--- a/content-pipeline/inputs/book04/b04_ch10_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch10_final.xlsx
@@ -541,7 +541,7 @@
         <is>
           <t>三上 ：觀看花車巡遊 （第二十八頁）
 大年初一，我們一家人去觀看花車巡遊。一早就有人在鐘樓附近等候，佔據有利位置觀賞花車巡遊，更有很多攝影發燒友，一個個舉着攝影機，希望抓住精彩瞬間。
-這次的花車巡遊比往年更壯觀更精彩。鼓樂隊開路，隊伍浩浩蕩蕩地走來。我一眼就看到了隊伍中間巨大的鯉魚燈，它紅彤彤的，散發出濃鬱的中國傳統味道，樣子活靈活現，顯得格外喜慶。
+這次的花車巡遊比往年更壯觀更精彩。鼓樂隊開路，隊伍浩浩蕩蕩地走來。我一眼就看到了隊伍中間巨大的鯉魚燈，它紅彤彤的，散發出濃郁的中國傳統味道，樣子活靈活現，顯得格外喜慶。
 接着，十二輛華麗的花車，在俄羅斯管絃樂隊的帶領下緩緩駛來，與維港璀璨的燈海互相輝映，令人賞心悅目，兩旁的人們都歡呼起來，現場十分熱鬧。
 然後是身穿各式衣服的國際表演隊，他們各個拿出看家本領，向人們呈現繽紛節目：中國的少林功夫和雜技團的表演讓人歎為觀止；荷蘭的高蹺表演是小朋友最喜歡看的，他們一個個神情自若，踩在高蹺上走路如走平地一般，不得不讓人佩服；美國的啦啦隊和現代舞表演更是掀起一輪高潮，把場上的氣氛都帶動了起來，我都禁不住想要衝到前面去盡情舞蹈。香港的舞龍舞獅隊施展渾身解數，真的是龍騰虎躍，把新年的歡樂氣氛帶動起來，人們歡笑着，談論着，陶醉在喜氣洋洋的氣氛之中。
 花車離我們漸漸遠去了，但我還沉浸在歡樂的場面裏，心情久久不能平靜⋯⋯</t>
@@ -1165,7 +1165,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>濃鬱</t>
+          <t>濃郁</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
